--- a/GORRITI/Agosto/GORRITI-Agosto.xlsx
+++ b/GORRITI/Agosto/GORRITI-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A6B5D0-D8BB-426D-851E-29D457939FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B801AD-467D-4ED5-A092-CB1CC3BAA567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="241">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -663,15 +663,6 @@
     <t>Transf 14/07</t>
   </si>
   <si>
-    <t>Transf 15/07</t>
-  </si>
-  <si>
-    <t>Transf 14/7</t>
-  </si>
-  <si>
-    <t>Transf 07/07</t>
-  </si>
-  <si>
     <t>Doartero mano de obra reparacion de portero</t>
   </si>
   <si>
@@ -690,30 +681,18 @@
     <t>Transf 17/07</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrajeria Ayram </t>
-  </si>
-  <si>
     <t>EN MAY, JUNI, JULI NO SE DEBITA EL MANTENIMIENTO DE CUENTA</t>
   </si>
   <si>
     <t>Debito 10/07</t>
   </si>
   <si>
-    <t>PMC 10/07</t>
-  </si>
-  <si>
     <t>Debito 17/07</t>
   </si>
   <si>
     <t>Ascensores Lema - Provision y colocacion de 95mts de cable de acero para sistema de caida de frenos mecanico</t>
   </si>
   <si>
-    <t>Transf 28/07</t>
-  </si>
-  <si>
-    <t>Doartero 50% restante mano de obra trabajo caños ascendentes</t>
-  </si>
-  <si>
     <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton</t>
   </si>
   <si>
@@ -726,15 +705,6 @@
     <t>Debito 21/07</t>
   </si>
   <si>
-    <t>Doartero - compra de materiales obra caños ascendentes</t>
-  </si>
-  <si>
-    <t>Doartero - compra de materiales iluminacion</t>
-  </si>
-  <si>
-    <t>Sr Oscar - Pintura uf 59</t>
-  </si>
-  <si>
     <t>PRESUPUESTO LEMA</t>
   </si>
   <si>
@@ -748,6 +718,39 @@
   </si>
   <si>
     <t>Ingreso sin identificar ya identificado Diciembre 24</t>
+  </si>
+  <si>
+    <t>Doartero Mano de obra y materiales recubrimiento de caño bajada</t>
+  </si>
+  <si>
+    <t>Transf 22/08</t>
+  </si>
+  <si>
+    <t>Sanitarios roma - Materiales</t>
+  </si>
+  <si>
+    <t>Transf 19/08</t>
+  </si>
+  <si>
+    <t>Matafuegos FIRE - Recarga</t>
+  </si>
+  <si>
+    <t>Doartero Mano de obra cañeria principal de subida de tanque</t>
+  </si>
+  <si>
+    <t>Transf 18/08</t>
+  </si>
+  <si>
+    <t>PMC 12/08</t>
+  </si>
+  <si>
+    <t>Transf 11/08</t>
+  </si>
+  <si>
+    <t>Doartero Mano de obra reparacion y cambio de luces piso 13</t>
+  </si>
+  <si>
+    <t>Transf 01/08</t>
   </si>
 </sst>
 </file>
@@ -755,15 +758,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -1491,14 +1494,14 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1506,7 +1509,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1519,9 +1522,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1535,7 +1538,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1545,40 +1548,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1593,24 +1596,24 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1623,63 +1626,63 @@
     <xf numFmtId="2" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1694,27 +1697,27 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1727,49 +1730,49 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="23" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1789,38 +1792,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1833,15 +1826,41 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1853,29 +1872,14 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2245,27 +2249,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M135"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="190"/>
       <c r="B1" s="191"/>
       <c r="C1" s="192"/>
       <c r="D1" s="192"/>
       <c r="E1" s="193"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="189" t="s">
         <v>0</v>
@@ -2274,7 +2278,7 @@
       <c r="D2" s="189"/>
       <c r="E2" s="70"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
       <c r="B3" s="189" t="s">
         <v>1</v>
@@ -2283,7 +2287,7 @@
       <c r="D3" s="189"/>
       <c r="E3" s="70"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15"/>
       <c r="B4" s="194" t="s">
         <v>2</v>
@@ -2294,7 +2298,7 @@
       </c>
       <c r="E4" s="70"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
@@ -2305,7 +2309,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="19"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
@@ -2318,7 +2322,7 @@
       </c>
       <c r="E6" s="16"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>8</v>
       </c>
@@ -2329,57 +2333,57 @@
       </c>
       <c r="E7" s="19"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="211" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="218" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="212"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="212"/>
-      <c r="C11" s="212"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="215" t="s">
+      <c r="C9" s="209"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="209"/>
+      <c r="C11" s="209"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="220" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="212"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="212"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="209"/>
+      <c r="B17" s="209"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="209"/>
+      <c r="E17" s="209"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>11</v>
       </c>
@@ -2388,7 +2392,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>12</v>
       </c>
@@ -2397,7 +2401,7 @@
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
     </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>13</v>
       </c>
@@ -2408,21 +2412,21 @@
       </c>
       <c r="E23" s="152"/>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="156"/>
       <c r="E24" s="112"/>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="156"/>
       <c r="E25" s="112"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -2433,7 +2437,7 @@
       </c>
       <c r="E26" s="112"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2441,7 +2445,7 @@
       <c r="E27" s="112"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="56" t="s">
         <v>15</v>
       </c>
@@ -2452,12 +2456,12 @@
         <v>1271490</v>
       </c>
       <c r="E28" s="158"/>
-      <c r="G28" s="203">
+      <c r="G28" s="202">
         <f>D28+D30</f>
         <v>2313543</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>16</v>
       </c>
@@ -2467,12 +2471,12 @@
         <v>1042053</v>
       </c>
       <c r="E29" s="152"/>
-      <c r="G29" s="205">
+      <c r="G29" s="204">
         <f>700000</f>
         <v>700000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="56" t="s">
         <v>15</v>
       </c>
@@ -2483,14 +2487,14 @@
         <v>1042053</v>
       </c>
       <c r="E30" s="158"/>
-      <c r="G30" s="204">
+      <c r="G30" s="203">
         <f>G28-G29</f>
         <v>1613543</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B31" s="201"/>
       <c r="C31" s="201"/>
@@ -2498,14 +2502,14 @@
         <v>98440</v>
       </c>
       <c r="E31" s="182"/>
-      <c r="G31" s="204">
+      <c r="G31" s="203">
         <v>-500000</v>
       </c>
       <c r="H31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="56" t="s">
         <v>15</v>
       </c>
@@ -2516,12 +2520,12 @@
         <v>98440</v>
       </c>
       <c r="E32" s="158"/>
-      <c r="G32" s="204">
+      <c r="G32" s="203">
         <f>G30+G31</f>
         <v>1113543</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="50" t="s">
         <v>17</v>
       </c>
@@ -2534,7 +2538,7 @@
       </c>
       <c r="F33" s="20"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>18</v>
       </c>
@@ -2543,24 +2547,24 @@
       <c r="D34" s="161"/>
       <c r="E34" s="162"/>
     </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="214" t="s">
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="219" t="s">
         <v>202</v>
       </c>
-      <c r="B35" s="210"/>
+      <c r="B35" s="211"/>
       <c r="C35" s="182"/>
-      <c r="D35" s="156">
-        <v>60000</v>
+      <c r="D35" s="239">
+        <v>90000</v>
       </c>
       <c r="E35" s="181" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="213" t="s">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="210" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="216"/>
+      <c r="B36" s="213"/>
       <c r="C36" s="51"/>
       <c r="D36" s="156">
         <v>249000</v>
@@ -2570,7 +2574,7 @@
       </c>
       <c r="H36" s="136"/>
     </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
         <v>19</v>
       </c>
@@ -2579,10 +2583,10 @@
       <c r="D37" s="163"/>
       <c r="E37" s="164">
         <f>SUM(D35:D36)</f>
-        <v>309000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>339000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>20</v>
       </c>
@@ -2591,27 +2595,27 @@
       <c r="D38" s="165"/>
       <c r="E38" s="166"/>
     </row>
-    <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="209" t="s">
+    <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="212" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="210"/>
+      <c r="B39" s="211"/>
       <c r="C39" s="53"/>
       <c r="D39" s="188">
         <v>144149</v>
       </c>
       <c r="E39" s="167" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="209"/>
-      <c r="B40" s="210"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="212"/>
+      <c r="B40" s="211"/>
       <c r="C40" s="53"/>
       <c r="D40" s="168"/>
       <c r="E40" s="167"/>
     </row>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
         <v>22</v>
       </c>
@@ -2623,7 +2627,7 @@
         <v>144149</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>23</v>
       </c>
@@ -2632,21 +2636,21 @@
       <c r="D42" s="169"/>
       <c r="E42" s="170"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="51"/>
-      <c r="D43" s="202">
-        <v>2581613.04</v>
+      <c r="D43" s="238">
+        <v>1843741.12</v>
       </c>
       <c r="E43" s="171" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G43" s="136"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>208</v>
       </c>
@@ -2654,14 +2658,14 @@
         <v>25</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="168">
-        <v>202628.43</v>
+      <c r="D44" s="184">
+        <v>133047.14000000001</v>
       </c>
       <c r="E44" s="172" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2670,15 +2674,15 @@
         <v>26</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="168">
-        <v>365477.51</v>
+      <c r="D45" s="184">
+        <v>241435.09</v>
       </c>
       <c r="E45" s="172" t="str">
         <f>E44</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2687,15 +2691,15 @@
         <v>27</v>
       </c>
       <c r="C46" s="5"/>
-      <c r="D46" s="168">
-        <v>22514.27</v>
+      <c r="D46" s="184">
+        <v>14783.02</v>
       </c>
       <c r="E46" s="173" t="str">
         <f>E45</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="27" t="s">
         <v>28</v>
       </c>
@@ -2704,10 +2708,10 @@
       <c r="D47" s="174"/>
       <c r="E47" s="113">
         <f>SUM(D43:D46)</f>
-        <v>3172233.2500000005</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2233006.37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>29</v>
       </c>
@@ -2716,33 +2720,33 @@
       <c r="D48" s="169"/>
       <c r="E48" s="170"/>
     </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="168">
-        <v>918866.69</v>
+      <c r="D49" s="184">
+        <v>1002998.17</v>
       </c>
       <c r="E49" s="179" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B50" s="184"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="168">
-        <v>23882.62</v>
+      <c r="D50" s="184">
+        <v>23385.69</v>
       </c>
       <c r="E50" s="179" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>32</v>
       </c>
@@ -2753,50 +2757,50 @@
       </c>
       <c r="E51" s="175" t="str">
         <f>E50</f>
-        <v>Transf 07/07</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Transf 11/08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B52" s="184"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="168">
-        <v>12392.89</v>
+      <c r="D52" s="184">
+        <v>12432.23</v>
       </c>
       <c r="E52" s="179" t="str">
         <f>E51</f>
-        <v>Transf 07/07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>Transf 11/08</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>203</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="168">
-        <v>9890.09</v>
+      <c r="D53" s="184">
+        <v>5586.39</v>
       </c>
       <c r="E53" s="185" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>204</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="168">
-        <v>1474687.08</v>
+      <c r="D54" s="184">
+        <v>2046270.6</v>
       </c>
       <c r="E54" s="185" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>34</v>
       </c>
@@ -2806,30 +2810,30 @@
         <v>23728.51</v>
       </c>
       <c r="E55" s="185" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="209" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="212" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="210"/>
+      <c r="B56" s="211"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="168">
-        <v>2168902.4500000002</v>
+      <c r="D56" s="184">
+        <v>2168902.4</v>
       </c>
       <c r="E56" s="185" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="209"/>
-      <c r="B57" s="210"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="212"/>
+      <c r="B57" s="211"/>
       <c r="C57" s="154"/>
-      <c r="D57" s="206"/>
-      <c r="E57" s="207"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="205"/>
+      <c r="E57" s="206"/>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="27" t="s">
         <v>36</v>
       </c>
@@ -2838,10 +2842,10 @@
       <c r="D58" s="163"/>
       <c r="E58" s="113">
         <f>SUM(D49:D57)</f>
-        <v>4647098.55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5298052.209999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="33" t="s">
         <v>37</v>
       </c>
@@ -2850,33 +2854,33 @@
       <c r="D59" s="163"/>
       <c r="E59" s="176"/>
     </row>
-    <row r="60" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="213" t="s">
-        <v>228</v>
-      </c>
-      <c r="B60" s="210"/>
+    <row r="60" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="210" t="s">
+        <v>221</v>
+      </c>
+      <c r="B60" s="211"/>
       <c r="C60" s="54"/>
       <c r="D60" s="168">
         <v>48400</v>
       </c>
       <c r="E60" s="179" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B61" s="155"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="168">
-        <v>55700</v>
+      <c r="D61" s="184">
+        <v>56800</v>
       </c>
       <c r="E61" s="179" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>39</v>
       </c>
@@ -2886,115 +2890,115 @@
         <v>135000</v>
       </c>
       <c r="E62" s="180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="213" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63" s="216"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="210" t="s">
+        <v>220</v>
+      </c>
+      <c r="B63" s="213"/>
       <c r="C63" s="5"/>
       <c r="D63" s="168">
         <v>770000</v>
       </c>
       <c r="E63" s="180" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="213" t="s">
-        <v>232</v>
-      </c>
-      <c r="B64" s="216"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="210" t="s">
+        <v>235</v>
+      </c>
+      <c r="B64" s="213"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="168">
-        <v>40020.120000000003</v>
+      <c r="D64" s="141">
+        <v>300000</v>
       </c>
       <c r="E64" s="180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="213" t="s">
-        <v>227</v>
-      </c>
-      <c r="B65" s="216"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="210" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" s="213"/>
       <c r="C65" s="199"/>
-      <c r="D65" s="116">
+      <c r="D65" s="141">
         <v>300000</v>
       </c>
       <c r="E65" s="180" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="213" t="s">
-        <v>233</v>
-      </c>
-      <c r="B66" s="216"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="210" t="s">
+        <v>239</v>
+      </c>
+      <c r="B66" s="213"/>
       <c r="C66" s="51"/>
-      <c r="D66" s="116">
-        <v>125475</v>
+      <c r="D66" s="141">
+        <v>150000</v>
       </c>
       <c r="E66" s="180" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="213" t="s">
-        <v>214</v>
-      </c>
-      <c r="B67" s="210"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="210" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="211"/>
       <c r="C67" s="5"/>
       <c r="D67" s="116">
         <v>150000</v>
       </c>
       <c r="E67" s="180" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="213" t="s">
-        <v>216</v>
-      </c>
-      <c r="B68" s="216"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="210" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="213"/>
       <c r="C68" s="5"/>
       <c r="D68" s="116">
         <f>65050+57650</f>
         <v>122700</v>
       </c>
       <c r="E68" s="180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="197" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B69" s="198"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="116">
-        <v>390000</v>
+      <c r="D69" s="141">
+        <v>95706.73</v>
       </c>
       <c r="E69" s="180"/>
     </row>
-    <row r="70" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="209" t="s">
-        <v>220</v>
-      </c>
-      <c r="B70" s="210"/>
+    <row r="70" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="212" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" s="211"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="116">
-        <v>8000</v>
+      <c r="D70" s="141">
+        <v>481849.77</v>
       </c>
       <c r="E70" s="180" t="s">
-        <v>218</v>
-      </c>
-      <c r="I70" s="209"/>
-      <c r="J70" s="210"/>
-    </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="I70" s="212"/>
+      <c r="J70" s="211"/>
+    </row>
+    <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="27" t="s">
         <v>40</v>
       </c>
@@ -3003,10 +3007,10 @@
       <c r="D71" s="32"/>
       <c r="E71" s="177">
         <f>SUM(D60:D70)</f>
-        <v>2145295.12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2610456.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="33" t="s">
         <v>41</v>
       </c>
@@ -3015,7 +3019,7 @@
       <c r="D72" s="159"/>
       <c r="E72" s="176"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>41</v>
       </c>
@@ -3027,7 +3031,7 @@
       </c>
       <c r="E73" s="178"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>205</v>
       </c>
@@ -3036,10 +3040,10 @@
       <c r="D74" s="168"/>
       <c r="E74" s="118"/>
       <c r="G74" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="50" t="s">
         <v>19</v>
       </c>
@@ -3051,31 +3055,31 @@
         <v>156032.49</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="112"/>
       <c r="E76" s="120"/>
     </row>
-    <row r="77" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="219" t="s">
-        <v>238</v>
-      </c>
-      <c r="B77" s="220"/>
-      <c r="C77" s="220"/>
-      <c r="D77" s="221"/>
+    <row r="77" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="215" t="s">
+        <v>228</v>
+      </c>
+      <c r="B77" s="216"/>
+      <c r="C77" s="216"/>
+      <c r="D77" s="217"/>
       <c r="E77" s="121">
         <v>1500000</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="D78" s="122"/>
       <c r="E78" s="123"/>
       <c r="F78" s="42"/>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>42</v>
       </c>
@@ -3084,21 +3088,21 @@
       <c r="D79" s="124"/>
       <c r="E79" s="200">
         <f>(SUM(E30:E77))</f>
-        <v>14485791.410000002</v>
+        <v>14692679.569999998</v>
       </c>
       <c r="F79" s="151"/>
       <c r="G79" s="42"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D80" s="122"/>
       <c r="E80" s="122"/>
       <c r="G80" s="151"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D81" s="122"/>
       <c r="E81" s="122"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
         <v>43</v>
       </c>
@@ -3107,35 +3111,35 @@
       <c r="D82" s="125"/>
       <c r="E82" s="126"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="209"/>
-      <c r="B83" s="210"/>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="212"/>
+      <c r="B83" s="211"/>
       <c r="C83" s="5"/>
       <c r="D83" s="141"/>
       <c r="E83" s="114"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="209"/>
-      <c r="B84" s="210"/>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="212"/>
+      <c r="B84" s="211"/>
       <c r="C84" s="5"/>
       <c r="D84" s="116"/>
       <c r="E84" s="114"/>
     </row>
-    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="213"/>
-      <c r="B85" s="210"/>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="210"/>
+      <c r="B85" s="211"/>
       <c r="C85" s="5"/>
       <c r="D85" s="116"/>
       <c r="E85" s="114"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="115"/>
       <c r="B86" s="117"/>
       <c r="C86" s="5"/>
       <c r="D86" s="116"/>
       <c r="E86" s="114"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="48"/>
       <c r="B87" s="47"/>
       <c r="C87" s="47"/>
@@ -3145,9 +3149,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="28" t="s">
         <v>44</v>
       </c>
@@ -3156,8 +3160,8 @@
       <c r="D90" s="29"/>
       <c r="E90" s="111"/>
     </row>
-    <row r="91" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>45</v>
       </c>
@@ -3169,26 +3173,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="108" t="s">
         <v>46</v>
       </c>
       <c r="B94" s="109">
         <f>E79</f>
-        <v>14485791.410000002</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>14692679.569999998</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="108" t="s">
         <v>47</v>
       </c>
       <c r="B95" s="109">
         <f>E79-E77</f>
-        <v>12985791.410000002</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>13192679.569999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="108" t="s">
         <v>48</v>
       </c>
@@ -3197,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="108" t="s">
         <v>49</v>
       </c>
@@ -3206,60 +3210,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="217"/>
-      <c r="B99" s="212"/>
-      <c r="C99" s="212"/>
-      <c r="D99" s="212"/>
-      <c r="E99" s="212"/>
-    </row>
-    <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="212"/>
-      <c r="B100" s="212"/>
-      <c r="C100" s="212"/>
-      <c r="D100" s="212"/>
-      <c r="E100" s="212"/>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="212"/>
-      <c r="B101" s="212"/>
-      <c r="C101" s="212"/>
-      <c r="D101" s="212"/>
-      <c r="E101" s="212"/>
-    </row>
-    <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="208"/>
+      <c r="B99" s="209"/>
+      <c r="C99" s="209"/>
+      <c r="D99" s="209"/>
+      <c r="E99" s="209"/>
+    </row>
+    <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="209"/>
+      <c r="B100" s="209"/>
+      <c r="C100" s="209"/>
+      <c r="D100" s="209"/>
+      <c r="E100" s="209"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="209"/>
+      <c r="B101" s="209"/>
+      <c r="C101" s="209"/>
+      <c r="D101" s="209"/>
+      <c r="E101" s="209"/>
+    </row>
+    <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B103" s="137"/>
       <c r="C103" s="22"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="31"/>
       <c r="B104" s="58">
         <v>0</v>
       </c>
       <c r="C104" s="24"/>
     </row>
-    <row r="105" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>51</v>
       </c>
       <c r="B105" s="38">
         <f>PRORRATEO!I81</f>
-        <v>12524643.369999997</v>
+        <v>12230350.099999998</v>
       </c>
       <c r="C105" s="22"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23"/>
       <c r="B106" s="38">
         <v>0</v>
       </c>
       <c r="C106" s="22"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="23" t="s">
         <v>52</v>
       </c>
@@ -3269,29 +3273,29 @@
       </c>
       <c r="C107" s="22"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="46"/>
       <c r="C108" s="22"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="131" t="s">
         <v>53</v>
       </c>
       <c r="B109" s="46"/>
       <c r="C109" s="22"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="37" t="s">
         <v>54</v>
       </c>
       <c r="B110" s="46">
         <f>-B95</f>
-        <v>-12985791.410000002</v>
+        <v>-13192679.569999998</v>
       </c>
       <c r="C110" s="22"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="26" t="s">
         <v>55</v>
       </c>
@@ -3301,33 +3305,33 @@
       </c>
       <c r="C111" s="22"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B112" s="58">
         <f>SUM(B104:B111)</f>
-        <v>-461148.04000000469</v>
+        <v>-962329.47000000067</v>
       </c>
       <c r="C112" s="25"/>
       <c r="D112" s="42"/>
     </row>
-    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="39"/>
       <c r="C113" s="25"/>
       <c r="D113" s="42"/>
       <c r="E113" s="138"/>
       <c r="F113" s="139"/>
     </row>
-    <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="40"/>
       <c r="C114" s="25"/>
     </row>
-    <row r="115" spans="1:6" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="39"/>
       <c r="C115" s="35"/>
     </row>
-    <row r="116" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="143" t="s">
         <v>56</v>
       </c>
@@ -3337,16 +3341,16 @@
       <c r="C116" s="35"/>
       <c r="D116" s="45"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="53" t="s">
         <v>57</v>
       </c>
       <c r="B117" s="148">
         <f>-B95</f>
-        <v>-12985791.410000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-13192679.569999998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="53" t="s">
         <v>58</v>
       </c>
@@ -3355,7 +3359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="53" t="s">
         <v>59</v>
       </c>
@@ -3364,68 +3368,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="B120" s="208">
+        <v>229</v>
+      </c>
+      <c r="B120" s="207">
         <v>-112065.15</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="53" t="s">
         <v>60</v>
       </c>
       <c r="B121" s="149">
         <f>PRORRATEO!I81</f>
-        <v>12524643.369999997</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12230350.099999998</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="150" t="s">
         <v>61</v>
       </c>
       <c r="B122" s="186"/>
     </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="146" t="s">
         <v>62</v>
       </c>
       <c r="B123" s="147">
         <f>SUM(B116:C122)</f>
-        <v>-160998.50937697478</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-662179.93937697075</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="145"/>
       <c r="B124" s="145"/>
     </row>
-    <row r="125" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="218" t="s">
+    <row r="125" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="B126" s="212"/>
-      <c r="C126" s="212"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="212"/>
-      <c r="B127" s="212"/>
-      <c r="C127" s="212"/>
-    </row>
-    <row r="128" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="209"/>
+      <c r="C126" s="209"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="209"/>
+      <c r="B127" s="209"/>
+      <c r="C127" s="209"/>
+    </row>
+    <row r="128" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="128"/>
       <c r="B128" s="34"/>
       <c r="C128" s="34">
         <v>40000</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="128"/>
       <c r="B129" s="130"/>
       <c r="C129" s="39"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="43" t="s">
         <v>40</v>
       </c>
@@ -3435,49 +3439,39 @@
       </c>
       <c r="C130" s="44"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M131" s="8"/>
     </row>
-    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="217"/>
-      <c r="B132" s="212"/>
-      <c r="C132" s="212"/>
-      <c r="D132" s="212"/>
-      <c r="E132" s="212"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="212"/>
-      <c r="B133" s="212"/>
-      <c r="C133" s="212"/>
-      <c r="D133" s="212"/>
-      <c r="E133" s="212"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="212"/>
-      <c r="B134" s="212"/>
-      <c r="C134" s="212"/>
-      <c r="D134" s="212"/>
-      <c r="E134" s="212"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="212"/>
-      <c r="B135" s="212"/>
-      <c r="C135" s="212"/>
-      <c r="D135" s="212"/>
-      <c r="E135" s="212"/>
+    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="208"/>
+      <c r="B132" s="209"/>
+      <c r="C132" s="209"/>
+      <c r="D132" s="209"/>
+      <c r="E132" s="209"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="209"/>
+      <c r="B133" s="209"/>
+      <c r="C133" s="209"/>
+      <c r="D133" s="209"/>
+      <c r="E133" s="209"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="209"/>
+      <c r="B134" s="209"/>
+      <c r="C134" s="209"/>
+      <c r="D134" s="209"/>
+      <c r="E134" s="209"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="209"/>
+      <c r="B135" s="209"/>
+      <c r="C135" s="209"/>
+      <c r="D135" s="209"/>
+      <c r="E135" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A132:E135"/>
-    <mergeCell ref="A99:E101"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A126:C127"/>
-    <mergeCell ref="A77:D77"/>
     <mergeCell ref="I70:J70"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A67:B67"/>
@@ -3492,6 +3486,16 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A132:E135"/>
+    <mergeCell ref="A99:E101"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A126:C127"/>
+    <mergeCell ref="A77:D77"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3502,52 +3506,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="0.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="19" max="19" width="0.109375" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="209"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
+      <c r="N1" s="209"/>
+      <c r="O1" s="209"/>
+      <c r="P1" s="209"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3568,18 +3572,18 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="231">
         <f>U2</f>
         <v>14485791.410000002</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
+      <c r="Q2" s="209"/>
+      <c r="R2" s="209"/>
       <c r="S2" s="20"/>
       <c r="U2">
         <v>14485791.410000002</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3599,85 +3603,85 @@
       <c r="Q3" s="55"/>
       <c r="R3" s="59"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="226" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="228" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="221" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="221" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="223" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="225" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="221" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="227" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="232" t="s">
+      <c r="N4" s="225" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="226" t="s">
+      <c r="O4" s="232" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="235" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="230" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="222"/>
+      <c r="B5" s="229"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="224"/>
+      <c r="L5" s="224"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="224"/>
+      <c r="O5" s="233"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
-    </row>
-    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="229"/>
+      <c r="R5" s="222"/>
+    </row>
+    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>81</v>
       </c>
@@ -3740,7 +3744,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
@@ -3803,7 +3807,7 @@
       </c>
       <c r="T7" s="42"/>
     </row>
-    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>85</v>
       </c>
@@ -3865,7 +3869,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>88</v>
       </c>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="U9" s="42"/>
     </row>
-    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>88</v>
       </c>
@@ -3991,7 +3995,7 @@
       </c>
       <c r="U10" s="42"/>
     </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>89</v>
       </c>
@@ -4055,7 +4059,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>89</v>
       </c>
@@ -4119,7 +4123,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>94</v>
       </c>
@@ -4181,7 +4185,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>94</v>
       </c>
@@ -4247,7 +4251,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>99</v>
       </c>
@@ -4313,7 +4317,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>99</v>
       </c>
@@ -4374,7 +4378,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>102</v>
       </c>
@@ -4440,7 +4444,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>102</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>108</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>108</v>
       </c>
@@ -4639,7 +4643,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>113</v>
       </c>
@@ -4706,7 +4710,7 @@
       </c>
       <c r="U21" s="41"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>113</v>
       </c>
@@ -4772,7 +4776,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>118</v>
       </c>
@@ -4841,7 +4845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>118</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>122</v>
       </c>
@@ -4968,7 +4972,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>124</v>
       </c>
@@ -5032,7 +5036,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>126</v>
       </c>
@@ -5104,7 +5108,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
@@ -5167,7 +5171,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>131</v>
       </c>
@@ -5231,7 +5235,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>131</v>
       </c>
@@ -5295,7 +5299,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>131</v>
       </c>
@@ -5361,7 +5365,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>131</v>
       </c>
@@ -5424,7 +5428,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>131</v>
       </c>
@@ -5488,7 +5492,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>131</v>
       </c>
@@ -5554,7 +5558,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>131</v>
       </c>
@@ -5618,7 +5622,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>131</v>
       </c>
@@ -5684,7 +5688,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>131</v>
       </c>
@@ -5747,7 +5751,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>131</v>
       </c>
@@ -5811,7 +5815,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>131</v>
       </c>
@@ -5875,7 +5879,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>131</v>
       </c>
@@ -5941,7 +5945,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>131</v>
       </c>
@@ -6010,7 +6014,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="51"/>
       <c r="B42" s="63">
         <v>1</v>
@@ -6077,7 +6081,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="64">
         <v>2</v>
       </c>
@@ -6140,7 +6144,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="64">
         <v>2</v>
       </c>
@@ -6198,7 +6202,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="64">
         <v>2</v>
       </c>
@@ -6260,7 +6264,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="64">
         <v>3</v>
       </c>
@@ -6322,7 +6326,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="64">
         <v>3</v>
       </c>
@@ -6383,7 +6387,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="64">
         <v>3</v>
       </c>
@@ -6444,7 +6448,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="64">
         <v>4</v>
       </c>
@@ -6507,7 +6511,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="64">
         <v>4</v>
       </c>
@@ -6571,7 +6575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="64">
         <v>4</v>
       </c>
@@ -6631,7 +6635,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="64">
         <v>5</v>
       </c>
@@ -6694,7 +6698,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="64">
         <v>5</v>
       </c>
@@ -6757,7 +6761,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="64">
         <v>5</v>
       </c>
@@ -6820,7 +6824,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="64">
         <v>6</v>
       </c>
@@ -6881,7 +6885,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="64">
         <v>6</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="64">
         <v>6</v>
       </c>
@@ -7005,7 +7009,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="64">
         <v>7</v>
       </c>
@@ -7066,7 +7070,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="64">
         <v>7</v>
       </c>
@@ -7127,7 +7131,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="64">
         <v>7</v>
       </c>
@@ -7187,7 +7191,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="64">
         <v>8</v>
       </c>
@@ -7248,7 +7252,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="64">
         <v>8</v>
       </c>
@@ -7310,7 +7314,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64">
         <v>8</v>
       </c>
@@ -7371,7 +7375,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="64">
         <v>9</v>
       </c>
@@ -7396,16 +7400,16 @@
       </c>
       <c r="I64" s="73">
         <f>RESUMEN!D69</f>
-        <v>390000</v>
+        <v>95706.73</v>
       </c>
       <c r="J64" s="74"/>
       <c r="K64" s="75">
         <f t="shared" si="11"/>
-        <v>-271813.41000000003</v>
+        <v>22479.86</v>
       </c>
       <c r="L64" s="75">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>674.39580000000001</v>
       </c>
       <c r="M64" s="76">
         <v>0</v>
@@ -7419,22 +7423,22 @@
       </c>
       <c r="P64" s="79">
         <f t="shared" si="14"/>
-        <v>-133488.41</v>
+        <v>161479.59</v>
       </c>
       <c r="Q64" s="80">
         <f t="shared" si="15"/>
-        <v>-141497.41</v>
+        <v>171168.59</v>
       </c>
       <c r="R64" s="81">
         <f t="shared" si="16"/>
-        <v>-137493.41</v>
+        <v>166323.59</v>
       </c>
       <c r="S64" s="42">
         <f t="shared" si="18"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="64">
         <v>9</v>
       </c>
@@ -7495,7 +7499,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="64">
         <v>9</v>
       </c>
@@ -7559,7 +7563,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="64">
         <v>10</v>
       </c>
@@ -7625,7 +7629,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="64">
         <v>10</v>
       </c>
@@ -7688,7 +7692,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="64">
         <v>10</v>
       </c>
@@ -7749,7 +7753,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="64">
         <v>11</v>
       </c>
@@ -7810,7 +7814,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="64">
         <v>11</v>
       </c>
@@ -7870,7 +7874,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="64">
         <v>11</v>
       </c>
@@ -7930,7 +7934,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="64">
         <v>12</v>
       </c>
@@ -7991,7 +7995,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="64">
         <v>12</v>
       </c>
@@ -8052,7 +8056,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="64">
         <v>12</v>
       </c>
@@ -8113,7 +8117,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="64"/>
       <c r="C76" s="86"/>
       <c r="D76" s="86"/>
@@ -8133,7 +8137,7 @@
       <c r="R76" s="81"/>
       <c r="S76" s="42"/>
     </row>
-    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="64"/>
       <c r="C77" s="86"/>
       <c r="D77" s="86"/>
@@ -8153,7 +8157,7 @@
       <c r="R77" s="81"/>
       <c r="S77" s="42"/>
     </row>
-    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="64"/>
       <c r="C78" s="86"/>
       <c r="D78" s="86"/>
@@ -8173,7 +8177,7 @@
       <c r="R78" s="81"/>
       <c r="S78" s="42"/>
     </row>
-    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="97"/>
       <c r="C79" s="134"/>
       <c r="D79" s="87"/>
@@ -8193,7 +8197,7 @@
       <c r="R79" s="81"/>
       <c r="S79" s="42"/>
     </row>
-    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="64"/>
       <c r="C80" s="64"/>
       <c r="D80" s="64"/>
@@ -8213,7 +8217,7 @@
       <c r="R80" s="101"/>
       <c r="S80" s="42"/>
     </row>
-    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="102"/>
       <c r="C81" s="135"/>
       <c r="D81" s="103"/>
@@ -8229,7 +8233,7 @@
       </c>
       <c r="I81" s="61">
         <f>SUM(I6:I80)</f>
-        <v>12524643.369999997</v>
+        <v>12230350.099999998</v>
       </c>
       <c r="J81" s="52">
         <f>SUM(J6:J80)</f>
@@ -8237,7 +8241,7 @@
       </c>
       <c r="K81" s="61">
         <f>SUM(K6:K80)</f>
-        <v>5450880.4799999995</v>
+        <v>5745173.75</v>
       </c>
       <c r="L81" s="61"/>
       <c r="M81" s="61">
@@ -8254,108 +8258,116 @@
       </c>
       <c r="P81" s="106">
         <f>SUM(P6:P80)</f>
-        <v>20142661.850000001</v>
+        <v>20437629.850000001</v>
       </c>
       <c r="Q81" s="106">
         <f>SUM(Q6:Q80)</f>
-        <v>21351243.849999998</v>
+        <v>21663909.849999998</v>
       </c>
       <c r="R81" s="106"/>
     </row>
-    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E82" s="49"/>
       <c r="F82" s="49"/>
     </row>
-    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="208" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="212"/>
-      <c r="G84" s="212"/>
-      <c r="H84" s="212"/>
-      <c r="I84" s="212"/>
-      <c r="J84" s="212"/>
-      <c r="K84" s="212"/>
-      <c r="L84" s="212"/>
-      <c r="M84" s="212"/>
-      <c r="N84" s="212"/>
-      <c r="O84" s="212"/>
-      <c r="P84" s="212"/>
-    </row>
-    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
-      <c r="H85" s="212"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="212"/>
-      <c r="K85" s="212"/>
-      <c r="L85" s="212"/>
-      <c r="M85" s="212"/>
-      <c r="N85" s="212"/>
-      <c r="O85" s="212"/>
-      <c r="P85" s="212"/>
-    </row>
-    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="212"/>
-      <c r="F86" s="212"/>
-      <c r="G86" s="212"/>
-      <c r="H86" s="212"/>
-      <c r="I86" s="212"/>
-      <c r="J86" s="212"/>
-      <c r="K86" s="212"/>
-      <c r="L86" s="212"/>
-      <c r="M86" s="212"/>
-      <c r="N86" s="212"/>
-      <c r="O86" s="212"/>
-      <c r="P86" s="212"/>
-    </row>
-    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="212"/>
-      <c r="F87" s="212"/>
-      <c r="G87" s="212"/>
-      <c r="H87" s="212"/>
-      <c r="I87" s="212"/>
-      <c r="J87" s="212"/>
-      <c r="K87" s="212"/>
-      <c r="L87" s="212"/>
-      <c r="M87" s="212"/>
-      <c r="N87" s="212"/>
-      <c r="O87" s="212"/>
-      <c r="P87" s="212"/>
-    </row>
-    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="212"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
-    </row>
-    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="212"/>
-      <c r="F89" s="212"/>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
+      <c r="F84" s="209"/>
+      <c r="G84" s="209"/>
+      <c r="H84" s="209"/>
+      <c r="I84" s="209"/>
+      <c r="J84" s="209"/>
+      <c r="K84" s="209"/>
+      <c r="L84" s="209"/>
+      <c r="M84" s="209"/>
+      <c r="N84" s="209"/>
+      <c r="O84" s="209"/>
+      <c r="P84" s="209"/>
+    </row>
+    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E85" s="209"/>
+      <c r="F85" s="209"/>
+      <c r="G85" s="209"/>
+      <c r="H85" s="209"/>
+      <c r="I85" s="209"/>
+      <c r="J85" s="209"/>
+      <c r="K85" s="209"/>
+      <c r="L85" s="209"/>
+      <c r="M85" s="209"/>
+      <c r="N85" s="209"/>
+      <c r="O85" s="209"/>
+      <c r="P85" s="209"/>
+    </row>
+    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="209"/>
+      <c r="F86" s="209"/>
+      <c r="G86" s="209"/>
+      <c r="H86" s="209"/>
+      <c r="I86" s="209"/>
+      <c r="J86" s="209"/>
+      <c r="K86" s="209"/>
+      <c r="L86" s="209"/>
+      <c r="M86" s="209"/>
+      <c r="N86" s="209"/>
+      <c r="O86" s="209"/>
+      <c r="P86" s="209"/>
+    </row>
+    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="209"/>
+      <c r="F87" s="209"/>
+      <c r="G87" s="209"/>
+      <c r="H87" s="209"/>
+      <c r="I87" s="209"/>
+      <c r="J87" s="209"/>
+      <c r="K87" s="209"/>
+      <c r="L87" s="209"/>
+      <c r="M87" s="209"/>
+      <c r="N87" s="209"/>
+      <c r="O87" s="209"/>
+      <c r="P87" s="209"/>
+    </row>
+    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E88" s="209"/>
+      <c r="F88" s="209"/>
+      <c r="G88" s="209"/>
+      <c r="H88" s="209"/>
+      <c r="I88" s="209"/>
+      <c r="J88" s="209"/>
+      <c r="K88" s="209"/>
+      <c r="L88" s="209"/>
+      <c r="M88" s="209"/>
+      <c r="N88" s="209"/>
+      <c r="O88" s="209"/>
+      <c r="P88" s="209"/>
+    </row>
+    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E89" s="209"/>
+      <c r="F89" s="209"/>
+      <c r="G89" s="209"/>
+      <c r="H89" s="209"/>
+      <c r="I89" s="209"/>
+      <c r="J89" s="209"/>
+      <c r="K89" s="209"/>
+      <c r="L89" s="209"/>
+      <c r="M89" s="209"/>
+      <c r="N89" s="209"/>
+      <c r="O89" s="209"/>
+      <c r="P89" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8367,14 +8379,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -8384,9 +8388,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C5" s="136"/>
     </row>
   </sheetData>
@@ -8397,58 +8401,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B965EB00-CFEB-49D4-A088-2327BD05E9DF}">
   <dimension ref="A1:U89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5.28515625" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
-    <col min="19" max="19" width="0.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="19" max="19" width="0.109375" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="209"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
+      <c r="N1" s="209"/>
+      <c r="O1" s="209"/>
+      <c r="P1" s="209"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:21" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -8457,20 +8461,20 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="231">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="212"/>
-      <c r="R2" s="212"/>
+      <c r="Q2" s="209"/>
+      <c r="R2" s="209"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -8490,80 +8494,80 @@
       <c r="Q3" s="55"/>
       <c r="R3" s="59"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="226" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="228" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="221" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="221" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="223" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="225" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="221" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="227" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="225" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="232" t="s">
-        <v>236</v>
-      </c>
-      <c r="O4" s="226"/>
-      <c r="P4" s="222" t="s">
+      <c r="N4" s="225" t="s">
+        <v>226</v>
+      </c>
+      <c r="O4" s="232"/>
+      <c r="P4" s="230" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="235" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="230" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="222"/>
+      <c r="B5" s="229"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
-    </row>
-    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="224"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="224"/>
+      <c r="L5" s="224"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="224"/>
+      <c r="O5" s="233"/>
+      <c r="P5" s="237"/>
+      <c r="Q5" s="229"/>
+      <c r="R5" s="222"/>
+    </row>
+    <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>81</v>
       </c>
@@ -8615,7 +8619,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
@@ -8667,7 +8671,7 @@
       </c>
       <c r="T7" s="42"/>
     </row>
-    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>85</v>
       </c>
@@ -8718,7 +8722,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>88</v>
       </c>
@@ -8770,7 +8774,7 @@
       </c>
       <c r="U9" s="42"/>
     </row>
-    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>88</v>
       </c>
@@ -8822,7 +8826,7 @@
       </c>
       <c r="U10" s="42"/>
     </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>89</v>
       </c>
@@ -8875,7 +8879,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>89</v>
       </c>
@@ -8928,7 +8932,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>94</v>
       </c>
@@ -8979,7 +8983,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>94</v>
       </c>
@@ -9035,7 +9039,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>99</v>
       </c>
@@ -9091,7 +9095,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>99</v>
       </c>
@@ -9144,7 +9148,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>102</v>
       </c>
@@ -9199,7 +9203,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>102</v>
       </c>
@@ -9254,7 +9258,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>108</v>
       </c>
@@ -9312,7 +9316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>108</v>
       </c>
@@ -9365,7 +9369,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>113</v>
       </c>
@@ -9421,7 +9425,7 @@
       </c>
       <c r="U21" s="41"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>113</v>
       </c>
@@ -9476,7 +9480,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>118</v>
       </c>
@@ -9534,7 +9538,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>118</v>
       </c>
@@ -9587,7 +9591,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>122</v>
       </c>
@@ -9640,7 +9644,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>124</v>
       </c>
@@ -9693,7 +9697,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>126</v>
       </c>
@@ -9754,7 +9758,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
@@ -9807,7 +9811,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>131</v>
       </c>
@@ -9860,7 +9864,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>131</v>
       </c>
@@ -9913,7 +9917,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>131</v>
       </c>
@@ -9968,7 +9972,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>131</v>
       </c>
@@ -10021,7 +10025,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>131</v>
       </c>
@@ -10074,7 +10078,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>131</v>
       </c>
@@ -10129,7 +10133,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>131</v>
       </c>
@@ -10182,7 +10186,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>131</v>
       </c>
@@ -10237,7 +10241,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>131</v>
       </c>
@@ -10290,7 +10294,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>131</v>
       </c>
@@ -10343,7 +10347,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>131</v>
       </c>
@@ -10396,7 +10400,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>131</v>
       </c>
@@ -10451,7 +10455,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>131</v>
       </c>
@@ -10509,7 +10513,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="51"/>
       <c r="B42" s="63">
         <v>1</v>
@@ -10565,7 +10569,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="64">
         <v>2</v>
       </c>
@@ -10617,7 +10621,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="64">
         <v>2</v>
       </c>
@@ -10667,7 +10671,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="64">
         <v>2</v>
       </c>
@@ -10719,7 +10723,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="64">
         <v>3</v>
       </c>
@@ -10771,7 +10775,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="64">
         <v>3</v>
       </c>
@@ -10821,7 +10825,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="64">
         <v>3</v>
       </c>
@@ -10871,7 +10875,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="64">
         <v>4</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="64">
         <v>4</v>
       </c>
@@ -10976,7 +10980,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="64">
         <v>4</v>
       </c>
@@ -11028,7 +11032,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="64">
         <v>5</v>
       </c>
@@ -11080,7 +11084,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="64">
         <v>5</v>
       </c>
@@ -11132,7 +11136,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="64">
         <v>5</v>
       </c>
@@ -11184,7 +11188,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="64">
         <v>6</v>
       </c>
@@ -11234,7 +11238,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="64">
         <v>6</v>
       </c>
@@ -11287,7 +11291,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="64">
         <v>6</v>
       </c>
@@ -11337,7 +11341,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="64">
         <v>7</v>
       </c>
@@ -11387,7 +11391,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="64">
         <v>7</v>
       </c>
@@ -11437,7 +11441,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="64">
         <v>7</v>
       </c>
@@ -11489,7 +11493,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="64">
         <v>8</v>
       </c>
@@ -11539,7 +11543,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="64">
         <v>8</v>
       </c>
@@ -11591,7 +11595,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64">
         <v>8</v>
       </c>
@@ -11641,7 +11645,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="64">
         <v>9</v>
       </c>
@@ -11693,7 +11697,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="64">
         <v>9</v>
       </c>
@@ -11746,7 +11750,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="64">
         <v>9</v>
       </c>
@@ -11799,7 +11803,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="64">
         <v>10</v>
       </c>
@@ -11854,7 +11858,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="64">
         <v>10</v>
       </c>
@@ -11906,7 +11910,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="64">
         <v>10</v>
       </c>
@@ -11956,7 +11960,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="64">
         <v>11</v>
       </c>
@@ -12006,7 +12010,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="64">
         <v>11</v>
       </c>
@@ -12058,7 +12062,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="64">
         <v>11</v>
       </c>
@@ -12108,7 +12112,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="64">
         <v>12</v>
       </c>
@@ -12158,7 +12162,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="64">
         <v>12</v>
       </c>
@@ -12208,7 +12212,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="64">
         <v>12</v>
       </c>
@@ -12258,7 +12262,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="64"/>
       <c r="C76" s="86"/>
       <c r="D76" s="86"/>
@@ -12278,7 +12282,7 @@
       <c r="R76" s="81"/>
       <c r="S76" s="42"/>
     </row>
-    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="64"/>
       <c r="C77" s="86"/>
       <c r="D77" s="86"/>
@@ -12298,7 +12302,7 @@
       <c r="R77" s="81"/>
       <c r="S77" s="42"/>
     </row>
-    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:21" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="64"/>
       <c r="C78" s="86"/>
       <c r="D78" s="86"/>
@@ -12318,7 +12322,7 @@
       <c r="R78" s="81"/>
       <c r="S78" s="42"/>
     </row>
-    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="97"/>
       <c r="C79" s="134"/>
       <c r="D79" s="87"/>
@@ -12338,7 +12342,7 @@
       <c r="R79" s="81"/>
       <c r="S79" s="42"/>
     </row>
-    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="64"/>
       <c r="C80" s="64"/>
       <c r="D80" s="64"/>
@@ -12358,7 +12362,7 @@
       <c r="R80" s="101"/>
       <c r="S80" s="42"/>
     </row>
-    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="102"/>
       <c r="C81" s="135"/>
       <c r="D81" s="103"/>
@@ -12407,100 +12411,108 @@
       </c>
       <c r="R81" s="106"/>
     </row>
-    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E82" s="49"/>
       <c r="F82" s="49"/>
     </row>
-    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+    <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="208" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="212"/>
-      <c r="G84" s="212"/>
-      <c r="H84" s="212"/>
-      <c r="I84" s="212"/>
-      <c r="J84" s="212"/>
-      <c r="K84" s="212"/>
-      <c r="L84" s="212"/>
-      <c r="M84" s="212"/>
-      <c r="N84" s="212"/>
-      <c r="O84" s="212"/>
-      <c r="P84" s="212"/>
-    </row>
-    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
-      <c r="H85" s="212"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="212"/>
-      <c r="K85" s="212"/>
-      <c r="L85" s="212"/>
-      <c r="M85" s="212"/>
-      <c r="N85" s="212"/>
-      <c r="O85" s="212"/>
-      <c r="P85" s="212"/>
-    </row>
-    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="212"/>
-      <c r="F86" s="212"/>
-      <c r="G86" s="212"/>
-      <c r="H86" s="212"/>
-      <c r="I86" s="212"/>
-      <c r="J86" s="212"/>
-      <c r="K86" s="212"/>
-      <c r="L86" s="212"/>
-      <c r="M86" s="212"/>
-      <c r="N86" s="212"/>
-      <c r="O86" s="212"/>
-      <c r="P86" s="212"/>
-    </row>
-    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="212"/>
-      <c r="F87" s="212"/>
-      <c r="G87" s="212"/>
-      <c r="H87" s="212"/>
-      <c r="I87" s="212"/>
-      <c r="J87" s="212"/>
-      <c r="K87" s="212"/>
-      <c r="L87" s="212"/>
-      <c r="M87" s="212"/>
-      <c r="N87" s="212"/>
-      <c r="O87" s="212"/>
-      <c r="P87" s="212"/>
-    </row>
-    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="212"/>
-      <c r="F88" s="212"/>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
-    </row>
-    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="212"/>
-      <c r="F89" s="212"/>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
+      <c r="F84" s="209"/>
+      <c r="G84" s="209"/>
+      <c r="H84" s="209"/>
+      <c r="I84" s="209"/>
+      <c r="J84" s="209"/>
+      <c r="K84" s="209"/>
+      <c r="L84" s="209"/>
+      <c r="M84" s="209"/>
+      <c r="N84" s="209"/>
+      <c r="O84" s="209"/>
+      <c r="P84" s="209"/>
+    </row>
+    <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E85" s="209"/>
+      <c r="F85" s="209"/>
+      <c r="G85" s="209"/>
+      <c r="H85" s="209"/>
+      <c r="I85" s="209"/>
+      <c r="J85" s="209"/>
+      <c r="K85" s="209"/>
+      <c r="L85" s="209"/>
+      <c r="M85" s="209"/>
+      <c r="N85" s="209"/>
+      <c r="O85" s="209"/>
+      <c r="P85" s="209"/>
+    </row>
+    <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="209"/>
+      <c r="F86" s="209"/>
+      <c r="G86" s="209"/>
+      <c r="H86" s="209"/>
+      <c r="I86" s="209"/>
+      <c r="J86" s="209"/>
+      <c r="K86" s="209"/>
+      <c r="L86" s="209"/>
+      <c r="M86" s="209"/>
+      <c r="N86" s="209"/>
+      <c r="O86" s="209"/>
+      <c r="P86" s="209"/>
+    </row>
+    <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="209"/>
+      <c r="F87" s="209"/>
+      <c r="G87" s="209"/>
+      <c r="H87" s="209"/>
+      <c r="I87" s="209"/>
+      <c r="J87" s="209"/>
+      <c r="K87" s="209"/>
+      <c r="L87" s="209"/>
+      <c r="M87" s="209"/>
+      <c r="N87" s="209"/>
+      <c r="O87" s="209"/>
+      <c r="P87" s="209"/>
+    </row>
+    <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E88" s="209"/>
+      <c r="F88" s="209"/>
+      <c r="G88" s="209"/>
+      <c r="H88" s="209"/>
+      <c r="I88" s="209"/>
+      <c r="J88" s="209"/>
+      <c r="K88" s="209"/>
+      <c r="L88" s="209"/>
+      <c r="M88" s="209"/>
+      <c r="N88" s="209"/>
+      <c r="O88" s="209"/>
+      <c r="P88" s="209"/>
+    </row>
+    <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E89" s="209"/>
+      <c r="F89" s="209"/>
+      <c r="G89" s="209"/>
+      <c r="H89" s="209"/>
+      <c r="I89" s="209"/>
+      <c r="J89" s="209"/>
+      <c r="K89" s="209"/>
+      <c r="L89" s="209"/>
+      <c r="M89" s="209"/>
+      <c r="N89" s="209"/>
+      <c r="O89" s="209"/>
+      <c r="P89" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="A4:A5"/>
@@ -12513,14 +12525,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/GORRITI/Agosto/GORRITI-Agosto.xlsx
+++ b/GORRITI/Agosto/GORRITI-Agosto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\GORRITI\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B801AD-467D-4ED5-A092-CB1CC3BAA567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDFB36A-E9A5-40CE-BC5C-472080D62579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -648,18 +648,6 @@
     <t>MANTENIMIENTO DE CUENTA - NO SE DEBITO NUEVAMENTE</t>
   </si>
   <si>
-    <t>VTO 14/08</t>
-  </si>
-  <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JULIO</t>
-  </si>
-  <si>
-    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES JUNIO - SE DEBE JULIO</t>
-  </si>
-  <si>
     <t>Transf 14/07</t>
   </si>
   <si>
@@ -751,6 +739,18 @@
   </si>
   <si>
     <t>Transf 01/08</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES JULIO - SE DEBE AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -1802,18 +1802,29 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1826,41 +1837,15 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1872,14 +1857,29 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2314,7 +2314,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C6" s="196"/>
       <c r="D6" s="189" t="s">
@@ -2334,49 +2334,49 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="218" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="209"/>
+      <c r="B9" s="212" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="213"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
+      <c r="B10" s="213"/>
+      <c r="C10" s="213"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="209"/>
-      <c r="C11" s="209"/>
+      <c r="B11" s="213"/>
+      <c r="C11" s="213"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="220" t="s">
+      <c r="A14" s="216" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="213"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
+      <c r="A15" s="213"/>
+      <c r="B15" s="213"/>
+      <c r="C15" s="213"/>
+      <c r="D15" s="213"/>
+      <c r="E15" s="213"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
+      <c r="A16" s="213"/>
+      <c r="B16" s="213"/>
+      <c r="C16" s="213"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="213"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="209"/>
-      <c r="B17" s="209"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="209"/>
-      <c r="E17" s="209"/>
+      <c r="A17" s="213"/>
+      <c r="B17" s="213"/>
+      <c r="C17" s="213"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="213"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B31" s="201"/>
       <c r="C31" s="201"/>
@@ -2506,7 +2506,7 @@
         <v>-500000</v>
       </c>
       <c r="H31" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2548,29 +2548,29 @@
       <c r="E34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="219" t="s">
+      <c r="A35" s="215" t="s">
         <v>202</v>
       </c>
       <c r="B35" s="211"/>
       <c r="C35" s="182"/>
-      <c r="D35" s="239">
+      <c r="D35" s="209">
         <v>90000</v>
       </c>
       <c r="E35" s="181" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="210" t="s">
-        <v>209</v>
-      </c>
-      <c r="B36" s="213"/>
+      <c r="A36" s="214" t="s">
+        <v>240</v>
+      </c>
+      <c r="B36" s="217"/>
       <c r="C36" s="51"/>
       <c r="D36" s="156">
         <v>249000</v>
       </c>
       <c r="E36" s="181" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H36" s="136"/>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="E38" s="166"/>
     </row>
     <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="212" t="s">
+      <c r="A39" s="210" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="211"/>
@@ -2605,11 +2605,11 @@
         <v>144149</v>
       </c>
       <c r="E39" s="167" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="212"/>
+      <c r="A40" s="210"/>
       <c r="B40" s="211"/>
       <c r="C40" s="53"/>
       <c r="D40" s="168"/>
@@ -2642,17 +2642,17 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="51"/>
-      <c r="D43" s="238">
+      <c r="D43" s="208">
         <v>1843741.12</v>
       </c>
       <c r="E43" s="171" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G43" s="136"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>25</v>
@@ -2662,13 +2662,13 @@
         <v>133047.14000000001</v>
       </c>
       <c r="E44" s="172" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>26</v>
@@ -2685,7 +2685,7 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>27</v>
@@ -2730,7 +2730,7 @@
         <v>1002998.17</v>
       </c>
       <c r="E49" s="179" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2743,7 +2743,7 @@
         <v>23385.69</v>
       </c>
       <c r="E50" s="179" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2784,7 +2784,7 @@
         <v>5586.39</v>
       </c>
       <c r="E53" s="185" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2797,7 +2797,7 @@
         <v>2046270.6</v>
       </c>
       <c r="E54" s="185" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2810,11 +2810,11 @@
         <v>23728.51</v>
       </c>
       <c r="E55" s="185" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="212" t="s">
+      <c r="A56" s="210" t="s">
         <v>35</v>
       </c>
       <c r="B56" s="211"/>
@@ -2823,11 +2823,11 @@
         <v>2168902.4</v>
       </c>
       <c r="E56" s="185" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="212"/>
+      <c r="A57" s="210"/>
       <c r="B57" s="211"/>
       <c r="C57" s="154"/>
       <c r="D57" s="205"/>
@@ -2855,8 +2855,8 @@
       <c r="E59" s="176"/>
     </row>
     <row r="60" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="210" t="s">
-        <v>221</v>
+      <c r="A60" s="214" t="s">
+        <v>217</v>
       </c>
       <c r="B60" s="211"/>
       <c r="C60" s="54"/>
@@ -2864,7 +2864,7 @@
         <v>48400</v>
       </c>
       <c r="E60" s="179" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -2877,7 +2877,7 @@
         <v>56800</v>
       </c>
       <c r="E61" s="179" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2890,64 +2890,64 @@
         <v>135000</v>
       </c>
       <c r="E62" s="180" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="210" t="s">
-        <v>220</v>
-      </c>
-      <c r="B63" s="213"/>
+      <c r="A63" s="214" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="217"/>
       <c r="C63" s="5"/>
       <c r="D63" s="168">
         <v>770000</v>
       </c>
       <c r="E63" s="180" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="210" t="s">
-        <v>235</v>
-      </c>
-      <c r="B64" s="213"/>
+      <c r="A64" s="214" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="217"/>
       <c r="C64" s="5"/>
       <c r="D64" s="141">
         <v>300000</v>
       </c>
       <c r="E64" s="180" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="210" t="s">
-        <v>230</v>
-      </c>
-      <c r="B65" s="213"/>
+      <c r="A65" s="214" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="217"/>
       <c r="C65" s="199"/>
       <c r="D65" s="141">
         <v>300000</v>
       </c>
       <c r="E65" s="180" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="210" t="s">
-        <v>239</v>
-      </c>
-      <c r="B66" s="213"/>
+      <c r="A66" s="214" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="217"/>
       <c r="C66" s="51"/>
       <c r="D66" s="141">
         <v>150000</v>
       </c>
       <c r="E66" s="180" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="210" t="s">
-        <v>211</v>
+      <c r="A67" s="214" t="s">
+        <v>207</v>
       </c>
       <c r="B67" s="211"/>
       <c r="C67" s="5"/>
@@ -2955,26 +2955,26 @@
         <v>150000</v>
       </c>
       <c r="E67" s="180" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="210" t="s">
-        <v>213</v>
-      </c>
-      <c r="B68" s="213"/>
+      <c r="A68" s="214" t="s">
+        <v>209</v>
+      </c>
+      <c r="B68" s="217"/>
       <c r="C68" s="5"/>
       <c r="D68" s="116">
         <f>65050+57650</f>
         <v>122700</v>
       </c>
       <c r="E68" s="180" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="197" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B69" s="198"/>
       <c r="C69" s="5"/>
@@ -2984,8 +2984,8 @@
       <c r="E69" s="180"/>
     </row>
     <row r="70" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="212" t="s">
-        <v>234</v>
+      <c r="A70" s="210" t="s">
+        <v>230</v>
       </c>
       <c r="B70" s="211"/>
       <c r="C70" s="5"/>
@@ -2993,9 +2993,9 @@
         <v>481849.77</v>
       </c>
       <c r="E70" s="180" t="s">
-        <v>215</v>
-      </c>
-      <c r="I70" s="212"/>
+        <v>211</v>
+      </c>
+      <c r="I70" s="210"/>
       <c r="J70" s="211"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3040,7 +3040,7 @@
       <c r="D74" s="168"/>
       <c r="E74" s="118"/>
       <c r="G74" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3063,12 +3063,12 @@
       <c r="E76" s="120"/>
     </row>
     <row r="77" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="215" t="s">
-        <v>228</v>
-      </c>
-      <c r="B77" s="216"/>
-      <c r="C77" s="216"/>
-      <c r="D77" s="217"/>
+      <c r="A77" s="220" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" s="221"/>
+      <c r="C77" s="221"/>
+      <c r="D77" s="222"/>
       <c r="E77" s="121">
         <v>1500000</v>
       </c>
@@ -3112,21 +3112,21 @@
       <c r="E82" s="126"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="212"/>
+      <c r="A83" s="210"/>
       <c r="B83" s="211"/>
       <c r="C83" s="5"/>
       <c r="D83" s="141"/>
       <c r="E83" s="114"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="212"/>
+      <c r="A84" s="210"/>
       <c r="B84" s="211"/>
       <c r="C84" s="5"/>
       <c r="D84" s="116"/>
       <c r="E84" s="114"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="210"/>
+      <c r="A85" s="214"/>
       <c r="B85" s="211"/>
       <c r="C85" s="5"/>
       <c r="D85" s="116"/>
@@ -3212,25 +3212,25 @@
     </row>
     <row r="98" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="208"/>
-      <c r="B99" s="209"/>
-      <c r="C99" s="209"/>
-      <c r="D99" s="209"/>
-      <c r="E99" s="209"/>
+      <c r="A99" s="218"/>
+      <c r="B99" s="213"/>
+      <c r="C99" s="213"/>
+      <c r="D99" s="213"/>
+      <c r="E99" s="213"/>
     </row>
     <row r="100" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="209"/>
-      <c r="B100" s="209"/>
-      <c r="C100" s="209"/>
-      <c r="D100" s="209"/>
-      <c r="E100" s="209"/>
+      <c r="A100" s="213"/>
+      <c r="B100" s="213"/>
+      <c r="C100" s="213"/>
+      <c r="D100" s="213"/>
+      <c r="E100" s="213"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="209"/>
-      <c r="B101" s="209"/>
-      <c r="C101" s="209"/>
-      <c r="D101" s="209"/>
-      <c r="E101" s="209"/>
+      <c r="A101" s="213"/>
+      <c r="B101" s="213"/>
+      <c r="C101" s="213"/>
+      <c r="D101" s="213"/>
+      <c r="E101" s="213"/>
     </row>
     <row r="103" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="21" t="s">
@@ -3370,7 +3370,7 @@
     </row>
     <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="53" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B120" s="207">
         <v>-112065.15</v>
@@ -3406,16 +3406,16 @@
     </row>
     <row r="125" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="214" t="s">
+      <c r="A126" s="219" t="s">
         <v>63</v>
       </c>
-      <c r="B126" s="209"/>
-      <c r="C126" s="209"/>
+      <c r="B126" s="213"/>
+      <c r="C126" s="213"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="209"/>
-      <c r="B127" s="209"/>
-      <c r="C127" s="209"/>
+      <c r="A127" s="213"/>
+      <c r="B127" s="213"/>
+      <c r="C127" s="213"/>
     </row>
     <row r="128" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="128"/>
@@ -3443,35 +3443,45 @@
       <c r="M131" s="8"/>
     </row>
     <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="208"/>
-      <c r="B132" s="209"/>
-      <c r="C132" s="209"/>
-      <c r="D132" s="209"/>
-      <c r="E132" s="209"/>
+      <c r="A132" s="218"/>
+      <c r="B132" s="213"/>
+      <c r="C132" s="213"/>
+      <c r="D132" s="213"/>
+      <c r="E132" s="213"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A133" s="209"/>
-      <c r="B133" s="209"/>
-      <c r="C133" s="209"/>
-      <c r="D133" s="209"/>
-      <c r="E133" s="209"/>
+      <c r="A133" s="213"/>
+      <c r="B133" s="213"/>
+      <c r="C133" s="213"/>
+      <c r="D133" s="213"/>
+      <c r="E133" s="213"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A134" s="209"/>
-      <c r="B134" s="209"/>
-      <c r="C134" s="209"/>
-      <c r="D134" s="209"/>
-      <c r="E134" s="209"/>
+      <c r="A134" s="213"/>
+      <c r="B134" s="213"/>
+      <c r="C134" s="213"/>
+      <c r="D134" s="213"/>
+      <c r="E134" s="213"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="209"/>
-      <c r="B135" s="209"/>
-      <c r="C135" s="209"/>
-      <c r="D135" s="209"/>
-      <c r="E135" s="209"/>
+      <c r="A135" s="213"/>
+      <c r="B135" s="213"/>
+      <c r="C135" s="213"/>
+      <c r="D135" s="213"/>
+      <c r="E135" s="213"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A132:E135"/>
+    <mergeCell ref="A99:E101"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A126:C127"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="I70:J70"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A67:B67"/>
@@ -3486,16 +3496,6 @@
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A132:E135"/>
-    <mergeCell ref="A99:E101"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A126:C127"/>
-    <mergeCell ref="A77:D77"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3538,16 +3538,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="209"/>
-      <c r="O1" s="209"/>
-      <c r="P1" s="209"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="213"/>
+      <c r="P1" s="213"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3572,12 +3572,12 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="231">
+      <c r="P2" s="225">
         <f>U2</f>
         <v>14485791.410000002</v>
       </c>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="209"/>
+      <c r="Q2" s="213"/>
+      <c r="R2" s="213"/>
       <c r="S2" s="20"/>
       <c r="U2">
         <v>14485791.410000002</v>
@@ -3604,82 +3604,82 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="226" t="s">
+      <c r="A4" s="236" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="238" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="226" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="221" t="s">
+      <c r="E4" s="226" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="223" t="s">
+      <c r="F4" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="221" t="s">
+      <c r="G4" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="225" t="s">
+      <c r="H4" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="235" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="227" t="s">
+      <c r="K4" s="237" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="236" t="s">
+      <c r="M4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="225" t="s">
+      <c r="N4" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="232" t="s">
+      <c r="O4" s="227" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="235" t="s">
+      <c r="Q4" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="230" t="s">
+      <c r="R4" s="223" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="229"/>
+      <c r="A5" s="224"/>
+      <c r="B5" s="231"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="224"/>
-      <c r="L5" s="224"/>
-      <c r="M5" s="222"/>
-      <c r="N5" s="224"/>
-      <c r="O5" s="233"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="224"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="M5" s="224"/>
+      <c r="N5" s="234"/>
+      <c r="O5" s="228"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/08</v>
-      </c>
-      <c r="Q5" s="229"/>
-      <c r="R5" s="222"/>
+        <v>VTO 15/09</v>
+      </c>
+      <c r="Q5" s="231"/>
+      <c r="R5" s="224"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -8272,102 +8272,94 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="208" t="str">
+      <c r="E84" s="218" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="209"/>
-      <c r="G84" s="209"/>
-      <c r="H84" s="209"/>
-      <c r="I84" s="209"/>
-      <c r="J84" s="209"/>
-      <c r="K84" s="209"/>
-      <c r="L84" s="209"/>
-      <c r="M84" s="209"/>
-      <c r="N84" s="209"/>
-      <c r="O84" s="209"/>
-      <c r="P84" s="209"/>
+      <c r="F84" s="213"/>
+      <c r="G84" s="213"/>
+      <c r="H84" s="213"/>
+      <c r="I84" s="213"/>
+      <c r="J84" s="213"/>
+      <c r="K84" s="213"/>
+      <c r="L84" s="213"/>
+      <c r="M84" s="213"/>
+      <c r="N84" s="213"/>
+      <c r="O84" s="213"/>
+      <c r="P84" s="213"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E85" s="209"/>
-      <c r="F85" s="209"/>
-      <c r="G85" s="209"/>
-      <c r="H85" s="209"/>
-      <c r="I85" s="209"/>
-      <c r="J85" s="209"/>
-      <c r="K85" s="209"/>
-      <c r="L85" s="209"/>
-      <c r="M85" s="209"/>
-      <c r="N85" s="209"/>
-      <c r="O85" s="209"/>
-      <c r="P85" s="209"/>
+      <c r="E85" s="213"/>
+      <c r="F85" s="213"/>
+      <c r="G85" s="213"/>
+      <c r="H85" s="213"/>
+      <c r="I85" s="213"/>
+      <c r="J85" s="213"/>
+      <c r="K85" s="213"/>
+      <c r="L85" s="213"/>
+      <c r="M85" s="213"/>
+      <c r="N85" s="213"/>
+      <c r="O85" s="213"/>
+      <c r="P85" s="213"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E86" s="209"/>
-      <c r="F86" s="209"/>
-      <c r="G86" s="209"/>
-      <c r="H86" s="209"/>
-      <c r="I86" s="209"/>
-      <c r="J86" s="209"/>
-      <c r="K86" s="209"/>
-      <c r="L86" s="209"/>
-      <c r="M86" s="209"/>
-      <c r="N86" s="209"/>
-      <c r="O86" s="209"/>
-      <c r="P86" s="209"/>
+      <c r="E86" s="213"/>
+      <c r="F86" s="213"/>
+      <c r="G86" s="213"/>
+      <c r="H86" s="213"/>
+      <c r="I86" s="213"/>
+      <c r="J86" s="213"/>
+      <c r="K86" s="213"/>
+      <c r="L86" s="213"/>
+      <c r="M86" s="213"/>
+      <c r="N86" s="213"/>
+      <c r="O86" s="213"/>
+      <c r="P86" s="213"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="209"/>
-      <c r="F87" s="209"/>
-      <c r="G87" s="209"/>
-      <c r="H87" s="209"/>
-      <c r="I87" s="209"/>
-      <c r="J87" s="209"/>
-      <c r="K87" s="209"/>
-      <c r="L87" s="209"/>
-      <c r="M87" s="209"/>
-      <c r="N87" s="209"/>
-      <c r="O87" s="209"/>
-      <c r="P87" s="209"/>
+      <c r="E87" s="213"/>
+      <c r="F87" s="213"/>
+      <c r="G87" s="213"/>
+      <c r="H87" s="213"/>
+      <c r="I87" s="213"/>
+      <c r="J87" s="213"/>
+      <c r="K87" s="213"/>
+      <c r="L87" s="213"/>
+      <c r="M87" s="213"/>
+      <c r="N87" s="213"/>
+      <c r="O87" s="213"/>
+      <c r="P87" s="213"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E88" s="209"/>
-      <c r="F88" s="209"/>
-      <c r="G88" s="209"/>
-      <c r="H88" s="209"/>
-      <c r="I88" s="209"/>
-      <c r="J88" s="209"/>
-      <c r="K88" s="209"/>
-      <c r="L88" s="209"/>
-      <c r="M88" s="209"/>
-      <c r="N88" s="209"/>
-      <c r="O88" s="209"/>
-      <c r="P88" s="209"/>
+      <c r="E88" s="213"/>
+      <c r="F88" s="213"/>
+      <c r="G88" s="213"/>
+      <c r="H88" s="213"/>
+      <c r="I88" s="213"/>
+      <c r="J88" s="213"/>
+      <c r="K88" s="213"/>
+      <c r="L88" s="213"/>
+      <c r="M88" s="213"/>
+      <c r="N88" s="213"/>
+      <c r="O88" s="213"/>
+      <c r="P88" s="213"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="209"/>
-      <c r="F89" s="209"/>
-      <c r="G89" s="209"/>
-      <c r="H89" s="209"/>
-      <c r="I89" s="209"/>
-      <c r="J89" s="209"/>
-      <c r="K89" s="209"/>
-      <c r="L89" s="209"/>
-      <c r="M89" s="209"/>
-      <c r="N89" s="209"/>
-      <c r="O89" s="209"/>
-      <c r="P89" s="209"/>
+      <c r="E89" s="213"/>
+      <c r="F89" s="213"/>
+      <c r="G89" s="213"/>
+      <c r="H89" s="213"/>
+      <c r="I89" s="213"/>
+      <c r="J89" s="213"/>
+      <c r="K89" s="213"/>
+      <c r="L89" s="213"/>
+      <c r="M89" s="213"/>
+      <c r="N89" s="213"/>
+      <c r="O89" s="213"/>
+      <c r="P89" s="213"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8379,6 +8371,14 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -8433,16 +8433,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="209"/>
-      <c r="O1" s="209"/>
-      <c r="P1" s="209"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="213"/>
+      <c r="P1" s="213"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -8452,7 +8452,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -8461,17 +8461,17 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="231">
+      <c r="P2" s="225">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="209"/>
+      <c r="Q2" s="213"/>
+      <c r="R2" s="213"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8495,77 +8495,77 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="226" t="s">
+      <c r="A4" s="236" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="238" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="221" t="s">
+      <c r="D4" s="226" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="221" t="s">
+      <c r="E4" s="226" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="223" t="s">
+      <c r="F4" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="221" t="s">
+      <c r="G4" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="225" t="s">
+      <c r="H4" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="221" t="s">
+      <c r="I4" s="226" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="235" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="227" t="s">
+      <c r="K4" s="237" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="225" t="s">
+      <c r="L4" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="236" t="s">
+      <c r="M4" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="225" t="s">
-        <v>226</v>
-      </c>
-      <c r="O4" s="232"/>
-      <c r="P4" s="230" t="s">
+      <c r="N4" s="233" t="s">
+        <v>222</v>
+      </c>
+      <c r="O4" s="227"/>
+      <c r="P4" s="223" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="235" t="s">
+      <c r="Q4" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="230" t="s">
+      <c r="R4" s="223" t="s">
         <v>80</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="229"/>
+      <c r="A5" s="224"/>
+      <c r="B5" s="231"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="222"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="222"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="224"/>
-      <c r="L5" s="224"/>
-      <c r="M5" s="222"/>
-      <c r="N5" s="224"/>
-      <c r="O5" s="233"/>
-      <c r="P5" s="237"/>
-      <c r="Q5" s="229"/>
-      <c r="R5" s="222"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="224"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="M5" s="224"/>
+      <c r="N5" s="234"/>
+      <c r="O5" s="228"/>
+      <c r="P5" s="239"/>
+      <c r="Q5" s="231"/>
+      <c r="R5" s="224"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -12417,102 +12417,94 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="208" t="str">
+      <c r="E84" s="218" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="209"/>
-      <c r="G84" s="209"/>
-      <c r="H84" s="209"/>
-      <c r="I84" s="209"/>
-      <c r="J84" s="209"/>
-      <c r="K84" s="209"/>
-      <c r="L84" s="209"/>
-      <c r="M84" s="209"/>
-      <c r="N84" s="209"/>
-      <c r="O84" s="209"/>
-      <c r="P84" s="209"/>
+      <c r="F84" s="213"/>
+      <c r="G84" s="213"/>
+      <c r="H84" s="213"/>
+      <c r="I84" s="213"/>
+      <c r="J84" s="213"/>
+      <c r="K84" s="213"/>
+      <c r="L84" s="213"/>
+      <c r="M84" s="213"/>
+      <c r="N84" s="213"/>
+      <c r="O84" s="213"/>
+      <c r="P84" s="213"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E85" s="209"/>
-      <c r="F85" s="209"/>
-      <c r="G85" s="209"/>
-      <c r="H85" s="209"/>
-      <c r="I85" s="209"/>
-      <c r="J85" s="209"/>
-      <c r="K85" s="209"/>
-      <c r="L85" s="209"/>
-      <c r="M85" s="209"/>
-      <c r="N85" s="209"/>
-      <c r="O85" s="209"/>
-      <c r="P85" s="209"/>
+      <c r="E85" s="213"/>
+      <c r="F85" s="213"/>
+      <c r="G85" s="213"/>
+      <c r="H85" s="213"/>
+      <c r="I85" s="213"/>
+      <c r="J85" s="213"/>
+      <c r="K85" s="213"/>
+      <c r="L85" s="213"/>
+      <c r="M85" s="213"/>
+      <c r="N85" s="213"/>
+      <c r="O85" s="213"/>
+      <c r="P85" s="213"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E86" s="209"/>
-      <c r="F86" s="209"/>
-      <c r="G86" s="209"/>
-      <c r="H86" s="209"/>
-      <c r="I86" s="209"/>
-      <c r="J86" s="209"/>
-      <c r="K86" s="209"/>
-      <c r="L86" s="209"/>
-      <c r="M86" s="209"/>
-      <c r="N86" s="209"/>
-      <c r="O86" s="209"/>
-      <c r="P86" s="209"/>
+      <c r="E86" s="213"/>
+      <c r="F86" s="213"/>
+      <c r="G86" s="213"/>
+      <c r="H86" s="213"/>
+      <c r="I86" s="213"/>
+      <c r="J86" s="213"/>
+      <c r="K86" s="213"/>
+      <c r="L86" s="213"/>
+      <c r="M86" s="213"/>
+      <c r="N86" s="213"/>
+      <c r="O86" s="213"/>
+      <c r="P86" s="213"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="209"/>
-      <c r="F87" s="209"/>
-      <c r="G87" s="209"/>
-      <c r="H87" s="209"/>
-      <c r="I87" s="209"/>
-      <c r="J87" s="209"/>
-      <c r="K87" s="209"/>
-      <c r="L87" s="209"/>
-      <c r="M87" s="209"/>
-      <c r="N87" s="209"/>
-      <c r="O87" s="209"/>
-      <c r="P87" s="209"/>
+      <c r="E87" s="213"/>
+      <c r="F87" s="213"/>
+      <c r="G87" s="213"/>
+      <c r="H87" s="213"/>
+      <c r="I87" s="213"/>
+      <c r="J87" s="213"/>
+      <c r="K87" s="213"/>
+      <c r="L87" s="213"/>
+      <c r="M87" s="213"/>
+      <c r="N87" s="213"/>
+      <c r="O87" s="213"/>
+      <c r="P87" s="213"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E88" s="209"/>
-      <c r="F88" s="209"/>
-      <c r="G88" s="209"/>
-      <c r="H88" s="209"/>
-      <c r="I88" s="209"/>
-      <c r="J88" s="209"/>
-      <c r="K88" s="209"/>
-      <c r="L88" s="209"/>
-      <c r="M88" s="209"/>
-      <c r="N88" s="209"/>
-      <c r="O88" s="209"/>
-      <c r="P88" s="209"/>
+      <c r="E88" s="213"/>
+      <c r="F88" s="213"/>
+      <c r="G88" s="213"/>
+      <c r="H88" s="213"/>
+      <c r="I88" s="213"/>
+      <c r="J88" s="213"/>
+      <c r="K88" s="213"/>
+      <c r="L88" s="213"/>
+      <c r="M88" s="213"/>
+      <c r="N88" s="213"/>
+      <c r="O88" s="213"/>
+      <c r="P88" s="213"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E89" s="209"/>
-      <c r="F89" s="209"/>
-      <c r="G89" s="209"/>
-      <c r="H89" s="209"/>
-      <c r="I89" s="209"/>
-      <c r="J89" s="209"/>
-      <c r="K89" s="209"/>
-      <c r="L89" s="209"/>
-      <c r="M89" s="209"/>
-      <c r="N89" s="209"/>
-      <c r="O89" s="209"/>
-      <c r="P89" s="209"/>
+      <c r="E89" s="213"/>
+      <c r="F89" s="213"/>
+      <c r="G89" s="213"/>
+      <c r="H89" s="213"/>
+      <c r="I89" s="213"/>
+      <c r="J89" s="213"/>
+      <c r="K89" s="213"/>
+      <c r="L89" s="213"/>
+      <c r="M89" s="213"/>
+      <c r="N89" s="213"/>
+      <c r="O89" s="213"/>
+      <c r="P89" s="213"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="A4:A5"/>
@@ -12525,6 +12517,14 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
